--- a/output/test_supref_CRS620MI.xlsx
+++ b/output/test_supref_CRS620MI.xlsx
@@ -5472,7 +5472,11 @@
     </row>
     <row r="4" ht="15" customHeight="1" thickTop="1">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>163633</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>10</t>
@@ -5528,7 +5532,11 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>161488</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>10</t>
@@ -5552,7 +5560,11 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>161160</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>10</t>
@@ -5576,7 +5588,11 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>162316</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>10</t>
@@ -5604,7 +5620,11 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>163729</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>15</t>
@@ -5628,7 +5648,11 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>165963</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>10</t>
@@ -5652,7 +5676,11 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>166304</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>10</t>
@@ -5708,7 +5736,11 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>160203</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>10</t>
@@ -5768,7 +5800,11 @@
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>160203</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>10</t>
@@ -5792,7 +5828,11 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>168072</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>15</t>
@@ -5844,7 +5884,11 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>170225</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>10</t>
@@ -5964,7 +6008,11 @@
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>169790</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>10</t>
